--- a/mmkBelgeler/KU010 Grade Eşlemesi.xlsx
+++ b/mmkBelgeler/KU010 Grade Eşlemesi.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\myilmaz\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/begumyilmaz/Documents/okul/koç/4.2/bitirme/bitirmeRepoYeni/indr491/mmkBelgeler/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48D6640-FA30-C149-98EA-C511F1163153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26760" windowHeight="12390"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="42">
   <si>
     <t>CR</t>
   </si>
@@ -155,7 +156,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -308,6 +309,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="34">
@@ -672,10 +674,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -998,16 +1003,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C72"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I72"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>39</v>
       </c>
@@ -1018,7 +1023,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1029,7 +1034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1040,7 +1045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1051,7 +1056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1073,7 +1078,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1084,7 +1089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1095,7 +1100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -1106,7 +1111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1116,8 +1121,9 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1127,8 +1133,23 @@
       <c r="C11" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
@@ -1138,8 +1159,20 @@
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
@@ -1149,8 +1182,14 @@
       <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
@@ -1160,8 +1199,14 @@
       <c r="C14" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
@@ -1171,8 +1216,14 @@
       <c r="C15" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
@@ -1183,7 +1234,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>3</v>
       </c>
@@ -1194,7 +1245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
@@ -1205,7 +1256,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
@@ -1216,7 +1267,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>3</v>
       </c>
@@ -1227,7 +1278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>3</v>
       </c>
@@ -1238,7 +1289,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1249,7 +1300,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>16</v>
       </c>
@@ -1260,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
@@ -1271,7 +1322,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
@@ -1282,7 +1333,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,7 +1344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
@@ -1304,7 +1355,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
@@ -1315,7 +1366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
@@ -1326,7 +1377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
@@ -1337,7 +1388,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>16</v>
       </c>
@@ -1348,7 +1399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
@@ -1359,7 +1410,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
@@ -1370,7 +1421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>16</v>
       </c>
@@ -1381,7 +1432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>16</v>
       </c>
@@ -1392,7 +1443,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>16</v>
       </c>
@@ -1403,7 +1454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>16</v>
       </c>
@@ -1414,7 +1465,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>16</v>
       </c>
@@ -1425,7 +1476,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>16</v>
       </c>
@@ -1436,7 +1487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
@@ -1447,7 +1498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>16</v>
       </c>
@@ -1458,7 +1509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>16</v>
       </c>
@@ -1469,7 +1520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>16</v>
       </c>
@@ -1480,7 +1531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>16</v>
       </c>
@@ -1491,7 +1542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>16</v>
       </c>
@@ -1502,7 +1553,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>16</v>
       </c>
@@ -1513,7 +1564,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>16</v>
       </c>
@@ -1524,7 +1575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>16</v>
       </c>
@@ -1535,7 +1586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>16</v>
       </c>
@@ -1546,7 +1597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>16</v>
       </c>
@@ -1557,7 +1608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>16</v>
       </c>
@@ -1568,7 +1619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>16</v>
       </c>
@@ -1579,7 +1630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>16</v>
       </c>
@@ -1590,7 +1641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>35</v>
       </c>
@@ -1601,7 +1652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>35</v>
       </c>
@@ -1612,7 +1663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>35</v>
       </c>
@@ -1623,7 +1674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>35</v>
       </c>
@@ -1634,7 +1685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>35</v>
       </c>
@@ -1645,7 +1696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>35</v>
       </c>
@@ -1667,7 +1718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>35</v>
       </c>
@@ -1678,7 +1729,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>35</v>
       </c>
@@ -1689,7 +1740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>35</v>
       </c>
@@ -1700,7 +1751,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>35</v>
       </c>
@@ -1711,7 +1762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>35</v>
       </c>
@@ -1722,7 +1773,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>35</v>
       </c>
@@ -1733,7 +1784,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>35</v>
       </c>
@@ -1744,7 +1795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>35</v>
       </c>
@@ -1755,7 +1806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>35</v>
       </c>
@@ -1766,7 +1817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>35</v>
       </c>
@@ -1777,7 +1828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
         <v>35</v>
       </c>
@@ -1788,7 +1839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>35</v>
       </c>
@@ -1806,18 +1857,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
